--- a/config/xlsx/quests.xlsx
+++ b/config/xlsx/quests.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -878,6 +878,1126 @@
         <v>0</v>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>1001</v>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>D1·合成×1</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>周常第1天任务</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>1002</v>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>D1·生成×2</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>周常第1天任务</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>1003</v>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>D1·制作×3</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>周常第1天任务</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>1004</v>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>D1·出售×5</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>周常第1天任务</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>1005</v>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>D1·战斗×1</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>周常第1天任务</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>1006</v>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>D2·合成×2</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>周常第2天任务</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>1007</v>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>D2·生成×3</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>周常第2天任务</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>1008</v>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>D2·制作×1</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>周常第2天任务</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>1009</v>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>D2·出售×2</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>周常第2天任务</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>1010</v>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>D2·战斗×3</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>周常第2天任务</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="H23" s="3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>1011</v>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>D3·合成×5</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>周常第3天任务</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>1012</v>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>D3·生成×1</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>周常第3天任务</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>1013</v>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>D3·制作×1</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>周常第3天任务</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="n">
+        <v>1014</v>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>D3·出售×2</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>周常第3天任务</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n">
+        <v>1015</v>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>D3·战斗×3</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>周常第3天任务</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="n">
+        <v>1016</v>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>D4·合成×5</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>周常第4天任务</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>1017</v>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>D4·生成×1</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>周常第4天任务</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F30" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="n">
+        <v>1018</v>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>D4·制作×2</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>周常第4天任务</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="H31" s="3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>1019</v>
+      </c>
+      <c r="B32" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>D4·出售×3</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>周常第4天任务</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="n">
+        <v>1020</v>
+      </c>
+      <c r="B33" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>D4·战斗×1</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>周常第4天任务</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="n">
+        <v>1021</v>
+      </c>
+      <c r="B34" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>D5·合成×2</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>周常第5天任务</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F34" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="n">
+        <v>1022</v>
+      </c>
+      <c r="B35" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>D5·生成×3</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>周常第5天任务</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="H35" s="3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n">
+        <v>1023</v>
+      </c>
+      <c r="B36" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>D5·制作×5</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>周常第5天任务</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F36" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="n">
+        <v>1024</v>
+      </c>
+      <c r="B37" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>D5·出售×1</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>周常第5天任务</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G37" s="3" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="H37" s="3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="n">
+        <v>1025</v>
+      </c>
+      <c r="B38" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>D5·战斗×1</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>周常第5天任务</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F38" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G38" s="3" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="H38" s="3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="n">
+        <v>1026</v>
+      </c>
+      <c r="B39" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>D6·合成×2</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>周常第6天任务</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="H39" s="3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="n">
+        <v>1027</v>
+      </c>
+      <c r="B40" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>D6·生成×3</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>周常第6天任务</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F40" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G40" s="3" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="H40" s="3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="n">
+        <v>1028</v>
+      </c>
+      <c r="B41" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>D6·制作×5</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>周常第6天任务</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F41" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G41" s="3" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="H41" s="3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="n">
+        <v>1029</v>
+      </c>
+      <c r="B42" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>D6·出售×1</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>周常第6天任务</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F42" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G42" s="3" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="H42" s="3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="n">
+        <v>1030</v>
+      </c>
+      <c r="B43" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>D6·战斗×2</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>周常第6天任务</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G43" s="3" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="H43" s="3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="n">
+        <v>1031</v>
+      </c>
+      <c r="B44" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>D7·合成×3</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>周常第7天任务</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F44" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G44" s="3" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="H44" s="3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="n">
+        <v>1032</v>
+      </c>
+      <c r="B45" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>D7·生成×1</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>周常第7天任务</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F45" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G45" s="3" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="H45" s="3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="n">
+        <v>1033</v>
+      </c>
+      <c r="B46" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>D7·制作×2</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>周常第7天任务</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F46" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G46" s="3" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="H46" s="3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="n">
+        <v>1034</v>
+      </c>
+      <c r="B47" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>D7·出售×3</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>周常第7天任务</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F47" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G47" s="3" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="H47" s="3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="n">
+        <v>1035</v>
+      </c>
+      <c r="B48" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>D7·战斗×5</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>周常第7天任务</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F48" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G48" s="3" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="H48" s="3" t="n">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/config/xlsx/quests.xlsx
+++ b/config/xlsx/quests.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H48"/>
+  <dimension ref="A1:H47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -496,55 +496,55 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>1</v>
+        <v>101</v>
       </c>
       <c r="B2" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>合成新手</t>
+          <t>初次合成</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>完成5次合成</t>
+          <t>完成1次合成</t>
         </is>
       </c>
       <c r="E2" s="3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F2" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="H2" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B3" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>初次合成</t>
+          <t>合成能手</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>完成1次合成</t>
+          <t>完成10次合成</t>
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F3" s="3" t="n">
         <v>1</v>
@@ -560,23 +560,23 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B4" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>合成能手</t>
+          <t>合成大师</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>完成10次合成</t>
+          <t>完成50次合成</t>
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="F4" s="3" t="n">
         <v>1</v>
@@ -592,23 +592,23 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>103</v>
+        <v>201</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>合成大师</t>
+          <t>初次生成</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>完成50次合成</t>
+          <t>生成1个物品</t>
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="F5" s="3" t="n">
         <v>1</v>
@@ -624,19 +624,19 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>201</v>
+        <v>301</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>初次生成</t>
+          <t>初次制作</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>生成1个物品</t>
+          <t>完成1次制作</t>
         </is>
       </c>
       <c r="E6" s="3" t="n">
@@ -656,19 +656,19 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>301</v>
+        <v>401</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>初次制作</t>
+          <t>初次出售</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>完成1次制作</t>
+          <t>出售1个物品</t>
         </is>
       </c>
       <c r="E7" s="3" t="n">
@@ -688,19 +688,19 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>401</v>
+        <v>501</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>初次出售</t>
+          <t>初次战斗</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>出售1个物品</t>
+          <t>进行1次战斗</t>
         </is>
       </c>
       <c r="E8" s="3" t="n">
@@ -720,19 +720,19 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>初次战斗</t>
+          <t>清剿关卡</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>进行1次战斗</t>
+          <t>通关1个战斗关卡</t>
         </is>
       </c>
       <c r="E9" s="3" t="n">
@@ -752,19 +752,19 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>502</v>
+        <v>601</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>清剿关卡</t>
+          <t>突破境界</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>通关1个战斗关卡</t>
+          <t>完成1次突破</t>
         </is>
       </c>
       <c r="E10" s="3" t="n">
@@ -784,23 +784,23 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>601</v>
+        <v>701</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>突破境界</t>
+          <t>服药达人</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>完成1次突破</t>
+          <t>使用10次丹药</t>
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F11" s="3" t="n">
         <v>1</v>
@@ -816,23 +816,23 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>701</v>
+        <v>901</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>服药达人</t>
+          <t>周天初成</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>使用10次丹药</t>
+          <t>完成1次大周天</t>
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>1</v>
@@ -848,26 +848,26 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>901</v>
+        <v>1001</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>周天初成</t>
+          <t>D1·合成×1</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>完成1次大周天</t>
+          <t>周常第1天任务</t>
         </is>
       </c>
       <c r="E13" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
@@ -875,19 +875,19 @@
         </is>
       </c>
       <c r="H13" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>D1·合成×1</t>
+          <t>D1·生成×2</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
@@ -896,7 +896,7 @@
         </is>
       </c>
       <c r="E14" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F14" s="3" t="n">
         <v>2</v>
@@ -912,14 +912,14 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="B15" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>D1·生成×2</t>
+          <t>D1·制作×3</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
@@ -928,7 +928,7 @@
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F15" s="3" t="n">
         <v>2</v>
@@ -944,14 +944,14 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>D1·制作×3</t>
+          <t>D1·出售×5</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
@@ -960,7 +960,7 @@
         </is>
       </c>
       <c r="E16" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F16" s="3" t="n">
         <v>2</v>
@@ -976,14 +976,14 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="B17" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>D1·出售×5</t>
+          <t>D1·战斗×1</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
@@ -992,7 +992,7 @@
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F17" s="3" t="n">
         <v>2</v>
@@ -1008,23 +1008,23 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>D1·战斗×1</t>
+          <t>D2·合成×2</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>周常第1天任务</t>
+          <t>周常第2天任务</t>
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F18" s="3" t="n">
         <v>2</v>
@@ -1040,14 +1040,14 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="B19" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>D2·合成×2</t>
+          <t>D2·生成×3</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
@@ -1056,7 +1056,7 @@
         </is>
       </c>
       <c r="E19" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F19" s="3" t="n">
         <v>2</v>
@@ -1072,14 +1072,14 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>D2·生成×3</t>
+          <t>D2·制作×1</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
@@ -1088,7 +1088,7 @@
         </is>
       </c>
       <c r="E20" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F20" s="3" t="n">
         <v>2</v>
@@ -1104,14 +1104,14 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="B21" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>D2·制作×1</t>
+          <t>D2·出售×2</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
@@ -1120,7 +1120,7 @@
         </is>
       </c>
       <c r="E21" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F21" s="3" t="n">
         <v>2</v>
@@ -1136,14 +1136,14 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="B22" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>D2·出售×2</t>
+          <t>D2·战斗×3</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
@@ -1152,7 +1152,7 @@
         </is>
       </c>
       <c r="E22" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F22" s="3" t="n">
         <v>2</v>
@@ -1168,23 +1168,23 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="B23" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>D3·合成×5</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>周常第3天任务</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="n">
         <v>5</v>
-      </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>D2·战斗×3</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>周常第2天任务</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="n">
-        <v>3</v>
       </c>
       <c r="F23" s="3" t="n">
         <v>2</v>
@@ -1200,14 +1200,14 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="B24" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>D3·合成×5</t>
+          <t>D3·生成×1</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
@@ -1216,7 +1216,7 @@
         </is>
       </c>
       <c r="E24" s="3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F24" s="3" t="n">
         <v>2</v>
@@ -1232,14 +1232,14 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="B25" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>D3·生成×1</t>
+          <t>D3·制作×1</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
@@ -1264,14 +1264,14 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="B26" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>D3·制作×1</t>
+          <t>D3·出售×2</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
@@ -1280,7 +1280,7 @@
         </is>
       </c>
       <c r="E26" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F26" s="3" t="n">
         <v>2</v>
@@ -1296,14 +1296,14 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="B27" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>D3·出售×2</t>
+          <t>D3·战斗×3</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
@@ -1312,7 +1312,7 @@
         </is>
       </c>
       <c r="E27" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>2</v>
@@ -1328,23 +1328,23 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="B28" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>D4·合成×5</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>周常第4天任务</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="n">
         <v>5</v>
-      </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>D3·战斗×3</t>
-        </is>
-      </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>周常第3天任务</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="n">
-        <v>3</v>
       </c>
       <c r="F28" s="3" t="n">
         <v>2</v>
@@ -1360,14 +1360,14 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="B29" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>D4·合成×5</t>
+          <t>D4·生成×1</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
@@ -1376,7 +1376,7 @@
         </is>
       </c>
       <c r="E29" s="3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>2</v>
@@ -1392,14 +1392,14 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="B30" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>D4·生成×1</t>
+          <t>D4·制作×2</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
@@ -1408,7 +1408,7 @@
         </is>
       </c>
       <c r="E30" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F30" s="3" t="n">
         <v>2</v>
@@ -1424,23 +1424,23 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="B31" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>D4·出售×3</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>周常第4天任务</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="n">
         <v>3</v>
-      </c>
-      <c r="C31" s="3" t="inlineStr">
-        <is>
-          <t>D4·制作×2</t>
-        </is>
-      </c>
-      <c r="D31" s="3" t="inlineStr">
-        <is>
-          <t>周常第4天任务</t>
-        </is>
-      </c>
-      <c r="E31" s="3" t="n">
-        <v>2</v>
       </c>
       <c r="F31" s="3" t="n">
         <v>2</v>
@@ -1456,14 +1456,14 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="B32" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>D4·出售×3</t>
+          <t>D4·战斗×1</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
@@ -1472,7 +1472,7 @@
         </is>
       </c>
       <c r="E32" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F32" s="3" t="n">
         <v>2</v>
@@ -1488,23 +1488,23 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="B33" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>D4·战斗×1</t>
+          <t>D5·合成×2</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>周常第4天任务</t>
+          <t>周常第5天任务</t>
         </is>
       </c>
       <c r="E33" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F33" s="3" t="n">
         <v>2</v>
@@ -1520,14 +1520,14 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="B34" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>D5·合成×2</t>
+          <t>D5·生成×3</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
@@ -1536,7 +1536,7 @@
         </is>
       </c>
       <c r="E34" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F34" s="3" t="n">
         <v>2</v>
@@ -1552,14 +1552,14 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="B35" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>D5·生成×3</t>
+          <t>D5·制作×5</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
@@ -1568,7 +1568,7 @@
         </is>
       </c>
       <c r="E35" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F35" s="3" t="n">
         <v>2</v>
@@ -1584,14 +1584,14 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="B36" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>D5·制作×5</t>
+          <t>D5·出售×1</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
@@ -1600,7 +1600,7 @@
         </is>
       </c>
       <c r="E36" s="3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F36" s="3" t="n">
         <v>2</v>
@@ -1616,14 +1616,14 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="B37" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>D5·出售×1</t>
+          <t>D5·战斗×1</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
@@ -1648,23 +1648,23 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="B38" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>D5·战斗×1</t>
+          <t>D6·合成×2</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>周常第5天任务</t>
+          <t>周常第6天任务</t>
         </is>
       </c>
       <c r="E38" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F38" s="3" t="n">
         <v>2</v>
@@ -1680,14 +1680,14 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="B39" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>D6·合成×2</t>
+          <t>D6·生成×3</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
@@ -1696,7 +1696,7 @@
         </is>
       </c>
       <c r="E39" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F39" s="3" t="n">
         <v>2</v>
@@ -1712,14 +1712,14 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="B40" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>D6·生成×3</t>
+          <t>D6·制作×5</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="E40" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F40" s="3" t="n">
         <v>2</v>
@@ -1744,14 +1744,14 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="B41" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>D6·制作×5</t>
+          <t>D6·出售×1</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
@@ -1760,7 +1760,7 @@
         </is>
       </c>
       <c r="E41" s="3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F41" s="3" t="n">
         <v>2</v>
@@ -1776,14 +1776,14 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="B42" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>D6·出售×1</t>
+          <t>D6·战斗×2</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
@@ -1792,7 +1792,7 @@
         </is>
       </c>
       <c r="E42" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F42" s="3" t="n">
         <v>2</v>
@@ -1808,23 +1808,23 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="B43" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>D6·战斗×2</t>
+          <t>D7·合成×3</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>周常第6天任务</t>
+          <t>周常第7天任务</t>
         </is>
       </c>
       <c r="E43" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F43" s="3" t="n">
         <v>2</v>
@@ -1840,14 +1840,14 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="B44" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>D7·合成×3</t>
+          <t>D7·生成×1</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
@@ -1856,7 +1856,7 @@
         </is>
       </c>
       <c r="E44" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F44" s="3" t="n">
         <v>2</v>
@@ -1872,14 +1872,14 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="B45" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>D7·生成×1</t>
+          <t>D7·制作×2</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
@@ -1888,7 +1888,7 @@
         </is>
       </c>
       <c r="E45" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F45" s="3" t="n">
         <v>2</v>
@@ -1904,23 +1904,23 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="B46" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>D7·出售×3</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>周常第7天任务</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="n">
         <v>3</v>
-      </c>
-      <c r="C46" s="3" t="inlineStr">
-        <is>
-          <t>D7·制作×2</t>
-        </is>
-      </c>
-      <c r="D46" s="3" t="inlineStr">
-        <is>
-          <t>周常第7天任务</t>
-        </is>
-      </c>
-      <c r="E46" s="3" t="n">
-        <v>2</v>
       </c>
       <c r="F46" s="3" t="n">
         <v>2</v>
@@ -1936,14 +1936,14 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="B47" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>D7·出售×3</t>
+          <t>D7·战斗×5</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
@@ -1952,7 +1952,7 @@
         </is>
       </c>
       <c r="E47" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F47" s="3" t="n">
         <v>2</v>
@@ -1963,38 +1963,6 @@
         </is>
       </c>
       <c r="H47" s="3" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="n">
-        <v>1035</v>
-      </c>
-      <c r="B48" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="C48" s="3" t="inlineStr">
-        <is>
-          <t>D7·战斗×5</t>
-        </is>
-      </c>
-      <c r="D48" s="3" t="inlineStr">
-        <is>
-          <t>周常第7天任务</t>
-        </is>
-      </c>
-      <c r="E48" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="F48" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="G48" s="3" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="H48" s="3" t="n">
         <v>2</v>
       </c>
     </row>
